--- a/Results_experiment/exp_5/preds_1111122222222222.xlsx
+++ b/Results_experiment/exp_5/preds_1111122222222222.xlsx
@@ -1629,7 +1629,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D2">
-        <v>2.054637670516968</v>
+        <v>2.421438217163086</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1643,7 +1643,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D3">
-        <v>1.988823413848877</v>
+        <v>2.424849271774292</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1657,7 +1657,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D4">
-        <v>4.222780704498291</v>
+        <v>2.401163101196289</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1671,7 +1671,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D5">
-        <v>3.995560169219971</v>
+        <v>3.573976516723633</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1685,7 +1685,7 @@
         <v>19.29999923706055</v>
       </c>
       <c r="D6">
-        <v>11.81240653991699</v>
+        <v>11.11405944824219</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1699,7 +1699,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D7">
-        <v>6.329961776733398</v>
+        <v>5.847500801086426</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1713,7 +1713,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D8">
-        <v>9.833236694335938</v>
+        <v>8.584079742431641</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1727,7 +1727,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D9">
-        <v>2.050500869750977</v>
+        <v>2.365724563598633</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1741,7 +1741,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D10">
-        <v>4.839208126068115</v>
+        <v>4.098422527313232</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1755,7 +1755,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D11">
-        <v>2.013850927352905</v>
+        <v>2.371630191802979</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1769,7 +1769,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D12">
-        <v>5.91288423538208</v>
+        <v>5.12416934967041</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1783,7 +1783,7 @@
         <v>0.5</v>
       </c>
       <c r="D13">
-        <v>2.06291127204895</v>
+        <v>2.383489847183228</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1797,7 +1797,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D14">
-        <v>2.095937728881836</v>
+        <v>2.435985565185547</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1811,7 +1811,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D15">
-        <v>10.31849479675293</v>
+        <v>6.532773971557617</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1825,7 +1825,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D16">
-        <v>2.5428466796875</v>
+        <v>2.42427921295166</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1839,7 +1839,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D17">
-        <v>2.889990329742432</v>
+        <v>2.622473239898682</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1853,7 +1853,7 @@
         <v>10.5</v>
       </c>
       <c r="D18">
-        <v>5.937774181365967</v>
+        <v>5.786154747009277</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1867,7 +1867,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D19">
-        <v>6.508329391479492</v>
+        <v>4.638492584228516</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1881,7 +1881,7 @@
         <v>23</v>
       </c>
       <c r="D20">
-        <v>19.0306282043457</v>
+        <v>19.48543357849121</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1895,7 +1895,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D21">
-        <v>2.953439474105835</v>
+        <v>2.43208646774292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1909,7 +1909,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D22">
-        <v>4.473483085632324</v>
+        <v>7.407328605651855</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1923,7 +1923,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>12.36930370330811</v>
+        <v>12.45728206634521</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1937,7 +1937,7 @@
         <v>9.5</v>
       </c>
       <c r="D24">
-        <v>7.827953815460205</v>
+        <v>5.216774940490723</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1951,7 +1951,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D25">
-        <v>2.013896465301514</v>
+        <v>2.380434513092041</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1965,7 +1965,7 @@
         <v>22.20000076293945</v>
       </c>
       <c r="D26">
-        <v>16.81239700317383</v>
+        <v>16.83593940734863</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1979,7 +1979,7 @@
         <v>6.5</v>
       </c>
       <c r="D27">
-        <v>1.996191024780273</v>
+        <v>2.376118659973145</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1993,7 +1993,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="D28">
-        <v>11.06460094451904</v>
+        <v>10.66721725463867</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2007,7 +2007,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D29">
-        <v>10.28191566467285</v>
+        <v>9.062688827514648</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2021,7 +2021,7 @@
         <v>2</v>
       </c>
       <c r="D30">
-        <v>6.073754787445068</v>
+        <v>4.860430717468262</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2035,7 +2035,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D31">
-        <v>6.365938186645508</v>
+        <v>8.763270378112793</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2049,7 +2049,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D32">
-        <v>6.075506687164307</v>
+        <v>5.521302223205566</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2063,7 +2063,7 @@
         <v>26.39999961853027</v>
       </c>
       <c r="D33">
-        <v>20.15054702758789</v>
+        <v>17.16912078857422</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2077,7 +2077,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D34">
-        <v>6.41829252243042</v>
+        <v>6.087371826171875</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2091,7 +2091,7 @@
         <v>4.5</v>
       </c>
       <c r="D35">
-        <v>2.071908950805664</v>
+        <v>2.369985103607178</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>3.895247459411621</v>
+        <v>4.483432769775391</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2119,7 +2119,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D37">
-        <v>2.072768688201904</v>
+        <v>2.365300178527832</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2133,7 +2133,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D38">
-        <v>4.016781330108643</v>
+        <v>2.397201061248779</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2147,7 +2147,7 @@
         <v>26.5</v>
       </c>
       <c r="D39">
-        <v>19.38033103942871</v>
+        <v>16.2919864654541</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2161,7 +2161,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D40">
-        <v>2.209976673126221</v>
+        <v>2.421297073364258</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2175,7 +2175,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>2.789106369018555</v>
+        <v>2.820693969726562</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2189,7 +2189,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D42">
-        <v>2.825125217437744</v>
+        <v>2.721334457397461</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2203,7 +2203,7 @@
         <v>16.70000076293945</v>
       </c>
       <c r="D43">
-        <v>14.42042255401611</v>
+        <v>13.404052734375</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2217,7 +2217,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D44">
-        <v>6.44748067855835</v>
+        <v>4.112939357757568</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2231,7 +2231,7 @@
         <v>0.5</v>
       </c>
       <c r="D45">
-        <v>2.114699602127075</v>
+        <v>2.403157949447632</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2245,7 +2245,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D46">
-        <v>1.90589714050293</v>
+        <v>2.385354995727539</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2259,7 +2259,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D47">
-        <v>1.99065363407135</v>
+        <v>2.435883522033691</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2273,7 +2273,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D48">
-        <v>2.745854377746582</v>
+        <v>2.423497676849365</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2287,7 +2287,7 @@
         <v>9</v>
       </c>
       <c r="D49">
-        <v>7.279351711273193</v>
+        <v>8.155010223388672</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2301,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="D50">
-        <v>2.075903415679932</v>
+        <v>2.383872509002686</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2315,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>2.011805057525635</v>
+        <v>2.428775787353516</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2329,7 +2329,7 @@
         <v>4</v>
       </c>
       <c r="D52">
-        <v>2.646452903747559</v>
+        <v>2.440568923950195</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2343,7 +2343,7 @@
         <v>4.5</v>
       </c>
       <c r="D53">
-        <v>1.990465998649597</v>
+        <v>2.361950874328613</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2357,7 +2357,7 @@
         <v>0.5</v>
       </c>
       <c r="D54">
-        <v>4.603095531463623</v>
+        <v>4.569943904876709</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2371,7 +2371,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D55">
-        <v>5.08085298538208</v>
+        <v>2.572525024414062</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2385,7 +2385,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D56">
-        <v>6.119144916534424</v>
+        <v>6.414921760559082</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2399,7 +2399,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D57">
-        <v>17.13351440429688</v>
+        <v>18.67411613464355</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2413,7 +2413,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D58">
-        <v>8.526674270629883</v>
+        <v>8.379319190979004</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2427,7 +2427,7 @@
         <v>24.20000076293945</v>
       </c>
       <c r="D59">
-        <v>14.08260726928711</v>
+        <v>15.27066040039062</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2441,7 +2441,7 @@
         <v>24.39999961853027</v>
       </c>
       <c r="D60">
-        <v>16.70316886901855</v>
+        <v>16.92872619628906</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2455,7 +2455,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D61">
-        <v>2.013824462890625</v>
+        <v>2.572506427764893</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2469,7 +2469,7 @@
         <v>0.5</v>
       </c>
       <c r="D62">
-        <v>2.002841234207153</v>
+        <v>2.417812824249268</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2483,7 +2483,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D63">
-        <v>7.313448429107666</v>
+        <v>6.503068923950195</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2497,7 +2497,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D64">
-        <v>2.215168476104736</v>
+        <v>2.457485675811768</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2511,7 +2511,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D65">
-        <v>4.547121524810791</v>
+        <v>2.918858528137207</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2525,7 +2525,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D66">
-        <v>3.013416290283203</v>
+        <v>3.300463199615479</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2539,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>2.094775676727295</v>
+        <v>2.397952556610107</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2553,7 +2553,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D68">
-        <v>6.11406135559082</v>
+        <v>5.06273365020752</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2567,7 +2567,7 @@
         <v>4.5</v>
       </c>
       <c r="D69">
-        <v>4.345384120941162</v>
+        <v>2.902180671691895</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2581,7 +2581,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D70">
-        <v>4.124443054199219</v>
+        <v>2.608768939971924</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2595,7 +2595,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D71">
-        <v>2.032022953033447</v>
+        <v>2.513551712036133</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2609,7 +2609,7 @@
         <v>15</v>
       </c>
       <c r="D72">
-        <v>11.61855125427246</v>
+        <v>11.61794567108154</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2623,7 +2623,7 @@
         <v>8.5</v>
       </c>
       <c r="D73">
-        <v>9.123613357543945</v>
+        <v>9.262161254882812</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2637,7 +2637,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D74">
-        <v>3.957347393035889</v>
+        <v>2.400305271148682</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2651,7 +2651,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D75">
-        <v>10.30985832214355</v>
+        <v>8.589069366455078</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2665,7 +2665,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D76">
-        <v>1.941318035125732</v>
+        <v>2.391456604003906</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2679,7 +2679,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D77">
-        <v>2.914670944213867</v>
+        <v>2.503973484039307</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2693,7 +2693,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D78">
-        <v>3.352179050445557</v>
+        <v>2.431535720825195</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2707,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="D79">
-        <v>2.039405822753906</v>
+        <v>2.409813404083252</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2721,7 +2721,7 @@
         <v>8.5</v>
       </c>
       <c r="D80">
-        <v>4.650657653808594</v>
+        <v>6.141977310180664</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2735,7 +2735,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D81">
-        <v>3.02548885345459</v>
+        <v>2.504990100860596</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="D82">
-        <v>6.051973819732666</v>
+        <v>5.490259170532227</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2763,7 +2763,7 @@
         <v>34.79999923706055</v>
       </c>
       <c r="D83">
-        <v>13.43356323242188</v>
+        <v>12.74861240386963</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2777,7 +2777,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D84">
-        <v>2.61750316619873</v>
+        <v>2.42911958694458</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2791,7 +2791,7 @@
         <v>29</v>
       </c>
       <c r="D85">
-        <v>5.922412395477295</v>
+        <v>4.371976375579834</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2805,7 +2805,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="D86">
-        <v>1.942055940628052</v>
+        <v>2.400159358978271</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2819,7 +2819,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D87">
-        <v>2.007915496826172</v>
+        <v>2.410048961639404</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2833,7 +2833,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D88">
-        <v>9.396681785583496</v>
+        <v>6.951336860656738</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2847,7 +2847,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D89">
-        <v>10.38383102416992</v>
+        <v>11.33353328704834</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2861,7 +2861,7 @@
         <v>9</v>
       </c>
       <c r="D90">
-        <v>4.727763652801514</v>
+        <v>2.651690483093262</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2875,7 +2875,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D91">
-        <v>6.585458278656006</v>
+        <v>3.520968914031982</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2889,7 +2889,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D92">
-        <v>2.608712196350098</v>
+        <v>2.37287712097168</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2903,7 +2903,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D93">
-        <v>6.284966945648193</v>
+        <v>6.661876678466797</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2917,7 +2917,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D94">
-        <v>1.953328371047974</v>
+        <v>2.679020404815674</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2931,7 +2931,7 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>2.33570384979248</v>
+        <v>2.421938896179199</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2945,7 +2945,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D96">
-        <v>2.094208717346191</v>
+        <v>2.420215129852295</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2959,7 +2959,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D97">
-        <v>2.046857118606567</v>
+        <v>2.417312622070312</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2973,7 +2973,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D98">
-        <v>5.052001953125</v>
+        <v>3.092610836029053</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2987,7 +2987,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D99">
-        <v>1.936237096786499</v>
+        <v>2.412894725799561</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3001,7 +3001,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D100">
-        <v>1.984208941459656</v>
+        <v>2.366739749908447</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3015,7 +3015,7 @@
         <v>4</v>
       </c>
       <c r="D101">
-        <v>2.126030445098877</v>
+        <v>2.443294048309326</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3029,7 +3029,7 @@
         <v>5.5</v>
       </c>
       <c r="D102">
-        <v>2.080560922622681</v>
+        <v>2.378119945526123</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3043,7 +3043,7 @@
         <v>19.5</v>
       </c>
       <c r="D103">
-        <v>4.085254192352295</v>
+        <v>2.382157325744629</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3057,7 +3057,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D104">
-        <v>1.932051777839661</v>
+        <v>3.733595371246338</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3071,7 +3071,7 @@
         <v>21.5</v>
       </c>
       <c r="D105">
-        <v>13.66949081420898</v>
+        <v>14.22448062896729</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3085,7 +3085,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D106">
-        <v>2.369240760803223</v>
+        <v>2.368603706359863</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3099,7 +3099,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D107">
-        <v>5.412026882171631</v>
+        <v>5.443892478942871</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3113,7 +3113,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D108">
-        <v>3.08733081817627</v>
+        <v>2.399980068206787</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3127,7 +3127,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D109">
-        <v>2.027500629425049</v>
+        <v>2.405473232269287</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3141,7 +3141,7 @@
         <v>10.5</v>
       </c>
       <c r="D110">
-        <v>7.070665836334229</v>
+        <v>6.064459800720215</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3155,7 +3155,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D111">
-        <v>2.510717868804932</v>
+        <v>2.376297950744629</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3169,7 +3169,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D112">
-        <v>7.435143947601318</v>
+        <v>7.285987854003906</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3183,7 +3183,7 @@
         <v>18.5</v>
       </c>
       <c r="D113">
-        <v>7.890720367431641</v>
+        <v>8.918511390686035</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3197,7 +3197,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D114">
-        <v>21.99558258056641</v>
+        <v>20.6397590637207</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3211,7 +3211,7 @@
         <v>32.09999847412109</v>
       </c>
       <c r="D115">
-        <v>17.21557235717773</v>
+        <v>17.97772216796875</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3225,7 +3225,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D116">
-        <v>2.066338539123535</v>
+        <v>2.357997417449951</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3239,7 +3239,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D117">
-        <v>4.864955425262451</v>
+        <v>2.60586404800415</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3253,7 +3253,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D118">
-        <v>2.006861925125122</v>
+        <v>2.413187742233276</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3267,7 +3267,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D119">
-        <v>2.00868821144104</v>
+        <v>2.429059505462646</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3281,7 +3281,7 @@
         <v>43.59999847412109</v>
       </c>
       <c r="D120">
-        <v>26.63435363769531</v>
+        <v>20.79737091064453</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3295,7 +3295,7 @@
         <v>21.29999923706055</v>
       </c>
       <c r="D121">
-        <v>25.41601181030273</v>
+        <v>24.21575736999512</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3309,7 +3309,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D122">
-        <v>1.959932446479797</v>
+        <v>2.368877410888672</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3323,7 +3323,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D123">
-        <v>7.164342403411865</v>
+        <v>5.40693187713623</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3337,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="D124">
-        <v>3.896614551544189</v>
+        <v>3.241157054901123</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3351,7 +3351,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D125">
-        <v>2.317605018615723</v>
+        <v>2.641680717468262</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3365,7 +3365,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D126">
-        <v>7.938515186309814</v>
+        <v>7.097672462463379</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3379,7 +3379,7 @@
         <v>17.10000038146973</v>
       </c>
       <c r="D127">
-        <v>5.624755382537842</v>
+        <v>6.56652307510376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3393,7 +3393,7 @@
         <v>8</v>
       </c>
       <c r="D128">
-        <v>4.419293880462646</v>
+        <v>4.506562232971191</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3407,7 +3407,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D129">
-        <v>2.08003830909729</v>
+        <v>2.438068389892578</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3421,7 +3421,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D130">
-        <v>3.677854061126709</v>
+        <v>3.464022159576416</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3435,7 +3435,7 @@
         <v>2</v>
       </c>
       <c r="D131">
-        <v>2.185802698135376</v>
+        <v>2.385931491851807</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3449,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="D132">
-        <v>5.049991607666016</v>
+        <v>4.695343971252441</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3463,7 +3463,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D133">
-        <v>2.098238229751587</v>
+        <v>2.401362895965576</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3477,7 +3477,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D134">
-        <v>2.073894500732422</v>
+        <v>2.418534278869629</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3491,7 +3491,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D135">
-        <v>2.481132507324219</v>
+        <v>2.406405925750732</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3505,7 +3505,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D136">
-        <v>1.983635067939758</v>
+        <v>2.434567451477051</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3519,7 +3519,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D137">
-        <v>10.6294994354248</v>
+        <v>9.578386306762695</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3533,7 +3533,7 @@
         <v>3.5</v>
       </c>
       <c r="D138">
-        <v>2.027539730072021</v>
+        <v>2.401912212371826</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3547,7 +3547,7 @@
         <v>8</v>
       </c>
       <c r="D139">
-        <v>6.473435878753662</v>
+        <v>5.266974449157715</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3561,7 +3561,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D140">
-        <v>1.943115949630737</v>
+        <v>2.373997688293457</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3575,7 +3575,7 @@
         <v>28.70000076293945</v>
       </c>
       <c r="D141">
-        <v>19.0305004119873</v>
+        <v>12.9834680557251</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3589,7 +3589,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D142">
-        <v>2.004800081253052</v>
+        <v>5.329739570617676</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3603,7 +3603,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D143">
-        <v>4.848928928375244</v>
+        <v>4.114783763885498</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3617,7 +3617,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D144">
-        <v>3.064762353897095</v>
+        <v>3.001156330108643</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3631,7 +3631,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D145">
-        <v>6.023459911346436</v>
+        <v>7.46996021270752</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3645,7 +3645,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D146">
-        <v>5.287093639373779</v>
+        <v>2.396782875061035</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3659,7 +3659,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D147">
-        <v>4.480386734008789</v>
+        <v>2.609882831573486</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3673,7 +3673,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D148">
-        <v>2.126904010772705</v>
+        <v>2.394810676574707</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3687,7 +3687,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D149">
-        <v>7.402018070220947</v>
+        <v>7.568553447723389</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3701,7 +3701,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D150">
-        <v>4.593515396118164</v>
+        <v>3.365588665008545</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3715,7 +3715,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D151">
-        <v>4.819671630859375</v>
+        <v>6.196481704711914</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3729,7 +3729,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D152">
-        <v>7.604422569274902</v>
+        <v>7.653779983520508</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3743,7 +3743,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D153">
-        <v>5.481292247772217</v>
+        <v>9.838179588317871</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3757,7 +3757,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D154">
-        <v>2.047463417053223</v>
+        <v>4.245829105377197</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3771,7 +3771,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D155">
-        <v>2.023626089096069</v>
+        <v>2.398414611816406</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>2.012177705764771</v>
+        <v>2.377933025360107</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3799,7 +3799,7 @@
         <v>26.29999923706055</v>
       </c>
       <c r="D157">
-        <v>16.98151206970215</v>
+        <v>16.48033905029297</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3813,7 +3813,7 @@
         <v>16</v>
       </c>
       <c r="D158">
-        <v>6.491993427276611</v>
+        <v>6.692695617675781</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3827,7 +3827,7 @@
         <v>0.5</v>
       </c>
       <c r="D159">
-        <v>1.896138548851013</v>
+        <v>3.710609912872314</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3841,7 +3841,7 @@
         <v>27.79999923706055</v>
       </c>
       <c r="D160">
-        <v>13.58999824523926</v>
+        <v>11.03661346435547</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3855,7 +3855,7 @@
         <v>41.79999923706055</v>
       </c>
       <c r="D161">
-        <v>14.8358268737793</v>
+        <v>12.12597751617432</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3869,7 +3869,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D162">
-        <v>1.981026768684387</v>
+        <v>2.428449630737305</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3883,7 +3883,7 @@
         <v>0.5</v>
       </c>
       <c r="D163">
-        <v>2.04856538772583</v>
+        <v>2.386313438415527</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3897,7 +3897,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D164">
-        <v>10.50465965270996</v>
+        <v>10.94251823425293</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3911,7 +3911,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D165">
-        <v>5.179717540740967</v>
+        <v>2.369054794311523</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3925,7 +3925,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D166">
-        <v>4.560078144073486</v>
+        <v>2.970656871795654</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3939,7 +3939,7 @@
         <v>5</v>
       </c>
       <c r="D167">
-        <v>2.114716529846191</v>
+        <v>2.635167598724365</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3953,7 +3953,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D168">
-        <v>3.857378959655762</v>
+        <v>2.432235717773438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3967,7 +3967,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D169">
-        <v>9.206377983093262</v>
+        <v>8.343138694763184</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3981,7 +3981,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D170">
-        <v>2.064988136291504</v>
+        <v>2.405805110931396</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3995,7 +3995,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D171">
-        <v>7.905948162078857</v>
+        <v>6.210695743560791</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4009,7 +4009,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D172">
-        <v>1.917996168136597</v>
+        <v>2.416515827178955</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4023,7 +4023,7 @@
         <v>18.20000076293945</v>
       </c>
       <c r="D173">
-        <v>13.77068519592285</v>
+        <v>12.77143383026123</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4037,7 +4037,7 @@
         <v>3</v>
       </c>
       <c r="D174">
-        <v>2.174012660980225</v>
+        <v>2.395912647247314</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4051,7 +4051,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D175">
-        <v>1.997994780540466</v>
+        <v>2.387746095657349</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4065,7 +4065,7 @@
         <v>14</v>
       </c>
       <c r="D176">
-        <v>8.837247848510742</v>
+        <v>8.974146842956543</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4079,7 +4079,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D177">
-        <v>2.979693412780762</v>
+        <v>2.491184711456299</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4093,7 +4093,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D178">
-        <v>10.06049060821533</v>
+        <v>8.736294746398926</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4107,7 +4107,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D179">
-        <v>4.453353881835938</v>
+        <v>5.455307006835938</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4121,7 +4121,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D180">
-        <v>13.83049869537354</v>
+        <v>12.7796049118042</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4135,7 +4135,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D181">
-        <v>2.084929943084717</v>
+        <v>2.40313720703125</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4149,7 +4149,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D182">
-        <v>2.088390827178955</v>
+        <v>2.382935047149658</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4163,7 +4163,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D183">
-        <v>7.431763172149658</v>
+        <v>2.926713466644287</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4177,7 +4177,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D184">
-        <v>6.780820369720459</v>
+        <v>4.955769062042236</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4191,7 +4191,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D185">
-        <v>1.945209145545959</v>
+        <v>2.407794952392578</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4205,7 +4205,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D186">
-        <v>1.925829887390137</v>
+        <v>2.438006401062012</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4219,7 +4219,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D187">
-        <v>8.545202255249023</v>
+        <v>7.878736972808838</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4233,7 +4233,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D188">
-        <v>2.010121583938599</v>
+        <v>2.376192092895508</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4247,7 +4247,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D189">
-        <v>2.022166728973389</v>
+        <v>2.378397941589355</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4261,7 +4261,7 @@
         <v>5.5</v>
       </c>
       <c r="D190">
-        <v>2.764842510223389</v>
+        <v>2.376401424407959</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4275,7 +4275,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D191">
-        <v>9.063276290893555</v>
+        <v>9.076877593994141</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4289,7 +4289,7 @@
         <v>2</v>
       </c>
       <c r="D192">
-        <v>2.145468235015869</v>
+        <v>2.383033275604248</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4303,7 +4303,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D193">
-        <v>3.372109413146973</v>
+        <v>2.954156398773193</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4317,7 +4317,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D194">
-        <v>3.24400806427002</v>
+        <v>2.456844329833984</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4331,7 +4331,7 @@
         <v>0.5</v>
       </c>
       <c r="D195">
-        <v>2.057278156280518</v>
+        <v>2.377544164657593</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4345,7 +4345,7 @@
         <v>32.59999847412109</v>
       </c>
       <c r="D196">
-        <v>21.94926452636719</v>
+        <v>19.71654319763184</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4359,7 +4359,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D197">
-        <v>11.96083641052246</v>
+        <v>8.597658157348633</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4373,7 +4373,7 @@
         <v>22.89999961853027</v>
       </c>
       <c r="D198">
-        <v>4.9773268699646</v>
+        <v>4.32485818862915</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4387,7 +4387,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="D199">
-        <v>15.40087890625</v>
+        <v>11.46019077301025</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4401,7 +4401,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D200">
-        <v>2.166604042053223</v>
+        <v>2.439867973327637</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4415,7 +4415,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D201">
-        <v>3.149641990661621</v>
+        <v>2.457876920700073</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4429,7 +4429,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D202">
-        <v>2.678126573562622</v>
+        <v>2.408917665481567</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4443,7 +4443,7 @@
         <v>4.5</v>
       </c>
       <c r="D203">
-        <v>2.031902074813843</v>
+        <v>3.187136650085449</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4457,7 +4457,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D204">
-        <v>9.451411247253418</v>
+        <v>7.999205589294434</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4471,7 +4471,7 @@
         <v>2.5</v>
       </c>
       <c r="D205">
-        <v>1.945194005966187</v>
+        <v>2.393710136413574</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4485,7 +4485,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D206">
-        <v>4.289068698883057</v>
+        <v>3.877565383911133</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4499,7 +4499,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D207">
-        <v>6.908178806304932</v>
+        <v>3.251577854156494</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4513,7 +4513,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D208">
-        <v>4.522921085357666</v>
+        <v>5.045158386230469</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4527,7 +4527,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D209">
-        <v>4.233741283416748</v>
+        <v>2.397911548614502</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4541,7 +4541,7 @@
         <v>4</v>
       </c>
       <c r="D210">
-        <v>4.623026847839355</v>
+        <v>4.38149356842041</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4555,7 +4555,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D211">
-        <v>4.112311363220215</v>
+        <v>5.950652122497559</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4569,7 +4569,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D212">
-        <v>5.046530723571777</v>
+        <v>3.723665237426758</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4583,7 +4583,7 @@
         <v>6</v>
       </c>
       <c r="D213">
-        <v>2.907638549804688</v>
+        <v>2.824037075042725</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4597,7 +4597,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D214">
-        <v>2.490261554718018</v>
+        <v>4.198645114898682</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4611,7 +4611,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D215">
-        <v>2.922268867492676</v>
+        <v>2.959202289581299</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4625,7 +4625,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D216">
-        <v>2.63386607170105</v>
+        <v>2.457761287689209</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4639,7 +4639,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D217">
-        <v>2.997369289398193</v>
+        <v>2.604349613189697</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4653,7 +4653,7 @@
         <v>5.5</v>
       </c>
       <c r="D218">
-        <v>2.823436260223389</v>
+        <v>4.478697299957275</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4667,7 +4667,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D219">
-        <v>2.030369281768799</v>
+        <v>2.40070915222168</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4681,7 +4681,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D220">
-        <v>2.162844181060791</v>
+        <v>2.410932540893555</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4695,7 +4695,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D221">
-        <v>1.999096632003784</v>
+        <v>2.383668422698975</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4709,7 +4709,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D222">
-        <v>7.724987983703613</v>
+        <v>7.657399654388428</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4723,7 +4723,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D223">
-        <v>7.367002010345459</v>
+        <v>5.227510929107666</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4737,7 +4737,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D224">
-        <v>2.032095670700073</v>
+        <v>2.401838302612305</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4751,7 +4751,7 @@
         <v>25.79999923706055</v>
       </c>
       <c r="D225">
-        <v>15.14605903625488</v>
+        <v>13.88537406921387</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4765,7 +4765,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D226">
-        <v>5.912420749664307</v>
+        <v>5.265449523925781</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4779,7 +4779,7 @@
         <v>12</v>
       </c>
       <c r="D227">
-        <v>3.047513961791992</v>
+        <v>3.481407165527344</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4793,7 +4793,7 @@
         <v>26.60000038146973</v>
       </c>
       <c r="D228">
-        <v>14.93945980072021</v>
+        <v>14.22243213653564</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4807,7 +4807,7 @@
         <v>17.70000076293945</v>
       </c>
       <c r="D229">
-        <v>12.8578405380249</v>
+        <v>13.74386119842529</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4821,7 +4821,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D230">
-        <v>4.07614278793335</v>
+        <v>5.485745429992676</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4835,7 +4835,7 @@
         <v>18.5</v>
       </c>
       <c r="D231">
-        <v>14.64950847625732</v>
+        <v>15.12946701049805</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4849,7 +4849,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D232">
-        <v>2.412116527557373</v>
+        <v>2.471174716949463</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4863,7 +4863,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D233">
-        <v>1.992325305938721</v>
+        <v>2.390737056732178</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4877,7 +4877,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D234">
-        <v>2.213643074035645</v>
+        <v>2.423033237457275</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4891,7 +4891,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D235">
-        <v>2.061749696731567</v>
+        <v>2.379055023193359</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4905,7 +4905,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D236">
-        <v>2.193860054016113</v>
+        <v>2.441686153411865</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4919,7 +4919,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D237">
-        <v>4.220664501190186</v>
+        <v>4.058667182922363</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4933,7 +4933,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D238">
-        <v>2.026402235031128</v>
+        <v>2.393338203430176</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4947,7 +4947,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D239">
-        <v>6.468192577362061</v>
+        <v>2.376930713653564</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4961,7 +4961,7 @@
         <v>5.5</v>
       </c>
       <c r="D240">
-        <v>4.660896778106689</v>
+        <v>2.485464811325073</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4975,7 +4975,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D241">
-        <v>3.535101413726807</v>
+        <v>3.930820941925049</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4989,7 +4989,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D242">
-        <v>2.453131675720215</v>
+        <v>2.443062782287598</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5003,7 +5003,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D243">
-        <v>1.97468090057373</v>
+        <v>2.372846603393555</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5017,7 +5017,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D244">
-        <v>1.968662858009338</v>
+        <v>2.387200355529785</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5031,7 +5031,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D245">
-        <v>2.055543422698975</v>
+        <v>2.477904796600342</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5045,7 +5045,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D246">
-        <v>4.599006652832031</v>
+        <v>3.368727207183838</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5059,7 +5059,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D247">
-        <v>2.030093908309937</v>
+        <v>2.415639400482178</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5073,7 +5073,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D248">
-        <v>5.077132225036621</v>
+        <v>4.755321502685547</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5087,7 +5087,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D249">
-        <v>3.34727668762207</v>
+        <v>2.41650915145874</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5101,7 +5101,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D250">
-        <v>3.066667318344116</v>
+        <v>2.380228042602539</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5115,7 +5115,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D251">
-        <v>5.268821239471436</v>
+        <v>5.359550476074219</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5129,7 +5129,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D252">
-        <v>2.057216644287109</v>
+        <v>2.376326084136963</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5143,7 +5143,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D253">
-        <v>1.972985506057739</v>
+        <v>2.561452388763428</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5157,7 +5157,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D254">
-        <v>7.740114688873291</v>
+        <v>8.104467391967773</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5171,7 +5171,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D255">
-        <v>4.617086410522461</v>
+        <v>4.888923645019531</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5185,7 +5185,7 @@
         <v>7.5</v>
       </c>
       <c r="D256">
-        <v>6.21862268447876</v>
+        <v>2.619081974029541</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5199,7 +5199,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D257">
-        <v>2.173320770263672</v>
+        <v>2.426811218261719</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5213,7 +5213,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D258">
-        <v>2.469333410263062</v>
+        <v>2.404098033905029</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5227,7 +5227,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D259">
-        <v>3.037056922912598</v>
+        <v>2.428723335266113</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5241,7 +5241,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>4.834450244903564</v>
+        <v>5.9641432762146</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5255,7 +5255,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D261">
-        <v>9.95948600769043</v>
+        <v>9.262035369873047</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5269,7 +5269,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D262">
-        <v>4.526986598968506</v>
+        <v>2.651511192321777</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5283,7 +5283,7 @@
         <v>3.5</v>
       </c>
       <c r="D263">
-        <v>2.545859575271606</v>
+        <v>2.453582286834717</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5297,7 +5297,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D264">
-        <v>2.114980936050415</v>
+        <v>2.356226444244385</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5311,7 +5311,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D265">
-        <v>13.76934242248535</v>
+        <v>7.039962768554688</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5325,7 +5325,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D266">
-        <v>2.044454097747803</v>
+        <v>2.354557514190674</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5339,7 +5339,7 @@
         <v>14</v>
       </c>
       <c r="D267">
-        <v>4.327374458312988</v>
+        <v>4.866605281829834</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5353,7 +5353,7 @@
         <v>3.5</v>
       </c>
       <c r="D268">
-        <v>3.102527141571045</v>
+        <v>2.693531274795532</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5367,7 +5367,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D269">
-        <v>5.762336254119873</v>
+        <v>7.323163986206055</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5381,7 +5381,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D270">
-        <v>2.026748895645142</v>
+        <v>2.450016260147095</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5395,7 +5395,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D271">
-        <v>2.903604984283447</v>
+        <v>2.513056755065918</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5409,7 +5409,7 @@
         <v>22.29999923706055</v>
       </c>
       <c r="D272">
-        <v>12.48643112182617</v>
+        <v>12.4655237197876</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5423,7 +5423,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D273">
-        <v>4.977640628814697</v>
+        <v>5.320382595062256</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5437,7 +5437,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D274">
-        <v>11.5864200592041</v>
+        <v>11.64280796051025</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5451,7 +5451,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D275">
-        <v>3.577273368835449</v>
+        <v>2.613799095153809</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5465,7 +5465,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D276">
-        <v>2.455934047698975</v>
+        <v>2.503530979156494</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5479,7 +5479,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D277">
-        <v>3.722090244293213</v>
+        <v>3.337272167205811</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5493,7 +5493,7 @@
         <v>5.5</v>
       </c>
       <c r="D278">
-        <v>2.029382228851318</v>
+        <v>2.423666954040527</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5507,7 +5507,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D279">
-        <v>2.336850643157959</v>
+        <v>2.385244369506836</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5521,7 +5521,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D280">
-        <v>10.74737739562988</v>
+        <v>15.4765625</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5535,7 +5535,7 @@
         <v>19</v>
       </c>
       <c r="D281">
-        <v>14.44774627685547</v>
+        <v>13.44110107421875</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5549,7 +5549,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D282">
-        <v>2.068413734436035</v>
+        <v>2.41319465637207</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5563,7 +5563,7 @@
         <v>2.5</v>
       </c>
       <c r="D283">
-        <v>2.059493064880371</v>
+        <v>2.413361310958862</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5577,7 +5577,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D284">
-        <v>2.083593368530273</v>
+        <v>2.363589763641357</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5591,7 +5591,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>1.986330270767212</v>
+        <v>4.954453945159912</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5605,7 +5605,7 @@
         <v>16.79999923706055</v>
       </c>
       <c r="D286">
-        <v>9.59844970703125</v>
+        <v>9.253264427185059</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5619,7 +5619,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D287">
-        <v>2.053550243377686</v>
+        <v>2.418851852416992</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5633,7 +5633,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D288">
-        <v>5.039962768554688</v>
+        <v>3.415019989013672</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5647,7 +5647,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D289">
-        <v>9.170004844665527</v>
+        <v>6.742310523986816</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5661,7 +5661,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D290">
-        <v>4.045633792877197</v>
+        <v>2.432316303253174</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5675,7 +5675,7 @@
         <v>27.39999961853027</v>
       </c>
       <c r="D291">
-        <v>17.28557586669922</v>
+        <v>17.43986320495605</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5689,7 +5689,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D292">
-        <v>4.288366317749023</v>
+        <v>2.446938514709473</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5703,7 +5703,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D293">
-        <v>2.114712715148926</v>
+        <v>2.39508581161499</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5717,7 +5717,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D294">
-        <v>4.44940710067749</v>
+        <v>2.442325115203857</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5731,7 +5731,7 @@
         <v>4</v>
       </c>
       <c r="D295">
-        <v>6.261669158935547</v>
+        <v>9.202668190002441</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5745,7 +5745,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D296">
-        <v>13.95818424224854</v>
+        <v>14.7518835067749</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5759,7 +5759,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D297">
-        <v>5.208688259124756</v>
+        <v>2.625149250030518</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5773,7 +5773,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D298">
-        <v>2.535478591918945</v>
+        <v>2.540526151657104</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5787,7 +5787,7 @@
         <v>20</v>
       </c>
       <c r="D299">
-        <v>15.13226890563965</v>
+        <v>14.17013454437256</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5801,7 +5801,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D300">
-        <v>10.96875953674316</v>
+        <v>11.40558338165283</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5815,7 +5815,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D301">
-        <v>3.535660743713379</v>
+        <v>3.465557098388672</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5829,7 +5829,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D302">
-        <v>3.197672843933105</v>
+        <v>2.420224905014038</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5843,7 +5843,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D303">
-        <v>2.044000864028931</v>
+        <v>2.436162948608398</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5857,7 +5857,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D304">
-        <v>2.037256717681885</v>
+        <v>2.351098299026489</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5871,7 +5871,7 @@
         <v>22.89999961853027</v>
       </c>
       <c r="D305">
-        <v>8.240095138549805</v>
+        <v>8.374414443969727</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5885,7 +5885,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D306">
-        <v>3.247398853302002</v>
+        <v>2.832385063171387</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5899,7 +5899,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D307">
-        <v>4.862021923065186</v>
+        <v>8.95667552947998</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5913,7 +5913,7 @@
         <v>3</v>
       </c>
       <c r="D308">
-        <v>2.094812870025635</v>
+        <v>2.403262853622437</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5927,7 +5927,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D309">
-        <v>4.69489049911499</v>
+        <v>2.5827317237854</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5941,7 +5941,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D310">
-        <v>2.014204502105713</v>
+        <v>2.412720680236816</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5955,7 +5955,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D311">
-        <v>1.991060495376587</v>
+        <v>2.392077445983887</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5969,7 +5969,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D312">
-        <v>1.971024513244629</v>
+        <v>2.661085605621338</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5983,7 +5983,7 @@
         <v>18</v>
       </c>
       <c r="D313">
-        <v>12.85906791687012</v>
+        <v>14.57387638092041</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5997,7 +5997,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D314">
-        <v>3.954485416412354</v>
+        <v>2.596162557601929</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6011,7 +6011,7 @@
         <v>1.5</v>
       </c>
       <c r="D315">
-        <v>1.999004244804382</v>
+        <v>2.415825128555298</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6025,7 +6025,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D316">
-        <v>2.130990982055664</v>
+        <v>3.383390426635742</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6039,7 +6039,7 @@
         <v>33.90000152587891</v>
       </c>
       <c r="D317">
-        <v>18.21902084350586</v>
+        <v>21.01706123352051</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6053,7 +6053,7 @@
         <v>19.89999961853027</v>
       </c>
       <c r="D318">
-        <v>13.14162635803223</v>
+        <v>13.70111560821533</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6067,7 +6067,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D319">
-        <v>4.049638271331787</v>
+        <v>5.308355331420898</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6081,7 +6081,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D320">
-        <v>3.236143112182617</v>
+        <v>3.060806751251221</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6095,7 +6095,7 @@
         <v>0.5</v>
       </c>
       <c r="D321">
-        <v>1.89604663848877</v>
+        <v>2.423967361450195</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6109,7 +6109,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D322">
-        <v>6.952074527740479</v>
+        <v>11.80997085571289</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6123,7 +6123,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D323">
-        <v>1.976479768753052</v>
+        <v>2.412405490875244</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6137,7 +6137,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D324">
-        <v>4.970456600189209</v>
+        <v>3.71688985824585</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6151,7 +6151,7 @@
         <v>8.5</v>
       </c>
       <c r="D325">
-        <v>3.08900260925293</v>
+        <v>2.431424617767334</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6165,7 +6165,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="D326">
-        <v>13.41949272155762</v>
+        <v>14.68832874298096</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6179,7 +6179,7 @@
         <v>11</v>
       </c>
       <c r="D327">
-        <v>6.660284996032715</v>
+        <v>3.2732834815979</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6193,7 +6193,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D328">
-        <v>4.830860614776611</v>
+        <v>2.488488674163818</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6207,7 +6207,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D329">
-        <v>2.339306831359863</v>
+        <v>2.483508586883545</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6221,7 +6221,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D330">
-        <v>7.090207576751709</v>
+        <v>4.68293571472168</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6235,7 +6235,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D331">
-        <v>2.188975811004639</v>
+        <v>2.509298801422119</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6249,7 +6249,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D332">
-        <v>3.366878032684326</v>
+        <v>2.391209602355957</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6263,7 +6263,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D333">
-        <v>2.004412651062012</v>
+        <v>2.396010637283325</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6277,7 +6277,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D334">
-        <v>1.953567028045654</v>
+        <v>2.362738609313965</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6291,7 +6291,7 @@
         <v>30.60000038146973</v>
       </c>
       <c r="D335">
-        <v>20.05238723754883</v>
+        <v>19.29461860656738</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6305,7 +6305,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D336">
-        <v>7.737012386322021</v>
+        <v>4.326144695281982</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6319,7 +6319,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D337">
-        <v>7.428632736206055</v>
+        <v>5.838315963745117</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6333,7 +6333,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D338">
-        <v>1.945126295089722</v>
+        <v>2.425375461578369</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6347,7 +6347,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D339">
-        <v>2.630277156829834</v>
+        <v>3.402232646942139</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6361,7 +6361,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D340">
-        <v>6.21579122543335</v>
+        <v>4.945136547088623</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6375,7 +6375,7 @@
         <v>24.20000076293945</v>
       </c>
       <c r="D341">
-        <v>32.14297485351562</v>
+        <v>25.83830451965332</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6389,7 +6389,7 @@
         <v>12.5</v>
       </c>
       <c r="D342">
-        <v>6.116795539855957</v>
+        <v>8.549590110778809</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6403,7 +6403,7 @@
         <v>34.5</v>
       </c>
       <c r="D343">
-        <v>16.60488891601562</v>
+        <v>18.54104423522949</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6417,7 +6417,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D344">
-        <v>2.000777721405029</v>
+        <v>2.388472557067871</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6431,7 +6431,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D345">
-        <v>3.079224109649658</v>
+        <v>3.701340198516846</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6445,7 +6445,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D346">
-        <v>2.409953594207764</v>
+        <v>2.461265563964844</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6459,7 +6459,7 @@
         <v>2.5</v>
       </c>
       <c r="D347">
-        <v>1.928588628768921</v>
+        <v>2.522500514984131</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6473,7 +6473,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D348">
-        <v>15.18107223510742</v>
+        <v>16.37428283691406</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6487,7 +6487,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D349">
-        <v>2.034025907516479</v>
+        <v>2.389931201934814</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6501,7 +6501,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D350">
-        <v>2.462255239486694</v>
+        <v>2.430330276489258</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6515,7 +6515,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D351">
-        <v>2.111319065093994</v>
+        <v>2.421817779541016</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6529,7 +6529,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D352">
-        <v>4.368264198303223</v>
+        <v>7.930006980895996</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6543,7 +6543,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D353">
-        <v>2.01750922203064</v>
+        <v>2.430909156799316</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6557,7 +6557,7 @@
         <v>18.5</v>
       </c>
       <c r="D354">
-        <v>13.70467472076416</v>
+        <v>14.55031871795654</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6571,7 +6571,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D355">
-        <v>2.229518890380859</v>
+        <v>3.207620143890381</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6585,7 +6585,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D356">
-        <v>1.92793869972229</v>
+        <v>2.402549982070923</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6599,7 +6599,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D357">
-        <v>3.516976356506348</v>
+        <v>3.357424259185791</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6613,7 +6613,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="D358">
-        <v>8.855907440185547</v>
+        <v>7.867897987365723</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6627,7 +6627,7 @@
         <v>19.5</v>
       </c>
       <c r="D359">
-        <v>11.62673473358154</v>
+        <v>10.46495151519775</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6641,7 +6641,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D360">
-        <v>2.159340620040894</v>
+        <v>2.413571834564209</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6655,7 +6655,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D361">
-        <v>2.078707695007324</v>
+        <v>2.373506546020508</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6669,7 +6669,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D362">
-        <v>2.626308917999268</v>
+        <v>2.533628463745117</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6683,7 +6683,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D363">
-        <v>4.556940078735352</v>
+        <v>4.807401657104492</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6697,7 +6697,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D364">
-        <v>5.211259365081787</v>
+        <v>3.004930973052979</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6711,7 +6711,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D365">
-        <v>5.742480754852295</v>
+        <v>4.998150825500488</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6725,7 +6725,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D366">
-        <v>7.101334095001221</v>
+        <v>7.44635534286499</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6739,7 +6739,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D367">
-        <v>2.031758785247803</v>
+        <v>2.369804620742798</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6753,7 +6753,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D368">
-        <v>2.035810470581055</v>
+        <v>3.243279933929443</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6767,7 +6767,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D369">
-        <v>8.534174919128418</v>
+        <v>9.142709732055664</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6781,7 +6781,7 @@
         <v>30.79999923706055</v>
       </c>
       <c r="D370">
-        <v>17.91997909545898</v>
+        <v>15.40208339691162</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6795,7 +6795,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D371">
-        <v>2.680306911468506</v>
+        <v>2.788741588592529</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6809,7 +6809,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D372">
-        <v>3.415047645568848</v>
+        <v>4.517279624938965</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6823,7 +6823,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D373">
-        <v>3.159735679626465</v>
+        <v>2.847554922103882</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6837,7 +6837,7 @@
         <v>4.5</v>
       </c>
       <c r="D374">
-        <v>2.573487758636475</v>
+        <v>2.492842197418213</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6851,7 +6851,7 @@
         <v>2.5</v>
       </c>
       <c r="D375">
-        <v>12.90302658081055</v>
+        <v>9.610769271850586</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6865,7 +6865,7 @@
         <v>31</v>
       </c>
       <c r="D376">
-        <v>14.17236709594727</v>
+        <v>12.44636344909668</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6879,7 +6879,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D377">
-        <v>2.062348127365112</v>
+        <v>2.402904033660889</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="D378">
-        <v>2.000794649124146</v>
+        <v>2.371816158294678</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6907,7 +6907,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D379">
-        <v>2.642333030700684</v>
+        <v>2.387914180755615</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6921,7 +6921,7 @@
         <v>5</v>
       </c>
       <c r="D380">
-        <v>4.433647632598877</v>
+        <v>2.431981801986694</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6935,7 +6935,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D381">
-        <v>3.393669605255127</v>
+        <v>3.110597372055054</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6949,7 +6949,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D382">
-        <v>8.8148193359375</v>
+        <v>10.68364429473877</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6963,7 +6963,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D383">
-        <v>7.22868537902832</v>
+        <v>2.718902587890625</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6977,7 +6977,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D384">
-        <v>10.8755931854248</v>
+        <v>10.20584106445312</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6991,7 +6991,7 @@
         <v>30.89999961853027</v>
       </c>
       <c r="D385">
-        <v>17.03073883056641</v>
+        <v>16.63761711120605</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -7005,7 +7005,7 @@
         <v>3</v>
       </c>
       <c r="D386">
-        <v>2.046020984649658</v>
+        <v>2.402607440948486</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -7019,7 +7019,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D387">
-        <v>3.98228645324707</v>
+        <v>3.214198112487793</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7033,7 +7033,7 @@
         <v>6</v>
       </c>
       <c r="D388">
-        <v>2.745728969573975</v>
+        <v>2.666106700897217</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7047,7 +7047,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D389">
-        <v>5.34467077255249</v>
+        <v>3.870535850524902</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7061,7 +7061,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D390">
-        <v>4.676424026489258</v>
+        <v>2.542887210845947</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7075,7 +7075,7 @@
         <v>3</v>
       </c>
       <c r="D391">
-        <v>6.735729694366455</v>
+        <v>5.969837665557861</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7089,7 +7089,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D392">
-        <v>2.640488624572754</v>
+        <v>2.647095203399658</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7103,7 +7103,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D393">
-        <v>2.130118846893311</v>
+        <v>2.359344005584717</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7117,7 +7117,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D394">
-        <v>2.517839431762695</v>
+        <v>2.368197441101074</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7131,7 +7131,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D395">
-        <v>4.549384117126465</v>
+        <v>2.452678203582764</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7145,7 +7145,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D396">
-        <v>2.106918334960938</v>
+        <v>2.427611351013184</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7159,7 +7159,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D397">
-        <v>3.728808879852295</v>
+        <v>5.306918621063232</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7173,7 +7173,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D398">
-        <v>3.514519214630127</v>
+        <v>2.554909944534302</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7187,7 +7187,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D399">
-        <v>10.21489715576172</v>
+        <v>7.499428749084473</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7201,7 +7201,7 @@
         <v>8</v>
       </c>
       <c r="D400">
-        <v>2.082539081573486</v>
+        <v>2.412147283554077</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7215,7 +7215,7 @@
         <v>11</v>
       </c>
       <c r="D401">
-        <v>5.799607753753662</v>
+        <v>4.177644729614258</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7229,7 +7229,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D402">
-        <v>2.616491317749023</v>
+        <v>2.563107967376709</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7243,7 +7243,7 @@
         <v>22.79999923706055</v>
       </c>
       <c r="D403">
-        <v>17.59391975402832</v>
+        <v>17.74519920349121</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7257,7 +7257,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D404">
-        <v>2.869858264923096</v>
+        <v>2.399589061737061</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7271,7 +7271,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D405">
-        <v>4.713864803314209</v>
+        <v>2.400277614593506</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7285,7 +7285,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D406">
-        <v>5.38418436050415</v>
+        <v>7.629186630249023</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7299,7 +7299,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D407">
-        <v>9.21183967590332</v>
+        <v>8.349363327026367</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7313,7 +7313,7 @@
         <v>2</v>
       </c>
       <c r="D408">
-        <v>2.934747695922852</v>
+        <v>2.399123430252075</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7327,7 +7327,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D409">
-        <v>2.109283447265625</v>
+        <v>2.358455657958984</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7341,7 +7341,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D410">
-        <v>2.038203001022339</v>
+        <v>2.368179798126221</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7355,7 +7355,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D411">
-        <v>2.009984493255615</v>
+        <v>2.352334976196289</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7369,7 +7369,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D412">
-        <v>1.978193283081055</v>
+        <v>2.398333549499512</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7383,7 +7383,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D413">
-        <v>3.060218811035156</v>
+        <v>3.287978649139404</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7397,7 +7397,7 @@
         <v>14.60000038146973</v>
       </c>
       <c r="D414">
-        <v>10.23085117340088</v>
+        <v>12.72974109649658</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7411,7 +7411,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D415">
-        <v>2.074310064315796</v>
+        <v>2.41402006149292</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7425,7 +7425,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D416">
-        <v>2.053082942962646</v>
+        <v>2.382354736328125</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7439,7 +7439,7 @@
         <v>9</v>
       </c>
       <c r="D417">
-        <v>4.058426380157471</v>
+        <v>3.719902038574219</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7453,7 +7453,7 @@
         <v>32.20000076293945</v>
       </c>
       <c r="D418">
-        <v>31.33934783935547</v>
+        <v>30.60777473449707</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7467,7 +7467,7 @@
         <v>21.29999923706055</v>
       </c>
       <c r="D419">
-        <v>15.45011901855469</v>
+        <v>15.53250980377197</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7481,7 +7481,7 @@
         <v>2</v>
       </c>
       <c r="D420">
-        <v>1.983957648277283</v>
+        <v>2.407979011535645</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7495,7 +7495,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D421">
-        <v>3.695468425750732</v>
+        <v>2.7345871925354</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7509,7 +7509,7 @@
         <v>18.20000076293945</v>
       </c>
       <c r="D422">
-        <v>9.202452659606934</v>
+        <v>9.185169219970703</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7523,7 +7523,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D423">
-        <v>2.026723146438599</v>
+        <v>2.364104747772217</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7537,7 +7537,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D424">
-        <v>2.053785085678101</v>
+        <v>2.412500381469727</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7551,7 +7551,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D425">
-        <v>2.399727821350098</v>
+        <v>2.504443645477295</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7565,7 +7565,7 @@
         <v>30.29999923706055</v>
       </c>
       <c r="D426">
-        <v>16.75612449645996</v>
+        <v>15.56283473968506</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7579,7 +7579,7 @@
         <v>16</v>
       </c>
       <c r="D427">
-        <v>8.655291557312012</v>
+        <v>10.17311954498291</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7593,7 +7593,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D428">
-        <v>2.013860464096069</v>
+        <v>2.356101512908936</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7607,7 +7607,7 @@
         <v>14.30000019073486</v>
       </c>
       <c r="D429">
-        <v>5.036135196685791</v>
+        <v>5.361984252929688</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7621,7 +7621,7 @@
         <v>11.5</v>
       </c>
       <c r="D430">
-        <v>7.361295223236084</v>
+        <v>6.040340423583984</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7635,7 +7635,7 @@
         <v>2.5</v>
       </c>
       <c r="D431">
-        <v>2.982486486434937</v>
+        <v>2.424984455108643</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7649,7 +7649,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D432">
-        <v>2.014465808868408</v>
+        <v>2.417426586151123</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7663,7 +7663,7 @@
         <v>4</v>
       </c>
       <c r="D433">
-        <v>2.997474670410156</v>
+        <v>2.443149566650391</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7677,7 +7677,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D434">
-        <v>2.183429002761841</v>
+        <v>2.526346206665039</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7691,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="D435">
-        <v>2.091976404190063</v>
+        <v>2.401834011077881</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7705,7 +7705,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D436">
-        <v>1.995482683181763</v>
+        <v>2.418023586273193</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7719,7 +7719,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D437">
-        <v>2.111388683319092</v>
+        <v>2.363410472869873</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7733,7 +7733,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D438">
-        <v>2.096233367919922</v>
+        <v>2.414008617401123</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7747,7 +7747,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D439">
-        <v>1.952437162399292</v>
+        <v>2.395512104034424</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7761,7 +7761,7 @@
         <v>2</v>
       </c>
       <c r="D440">
-        <v>2.087445259094238</v>
+        <v>2.404018878936768</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7775,7 +7775,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D441">
-        <v>3.237643718719482</v>
+        <v>2.393166542053223</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7789,7 +7789,7 @@
         <v>1</v>
       </c>
       <c r="D442">
-        <v>1.944498062133789</v>
+        <v>2.504333019256592</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7803,7 +7803,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D443">
-        <v>9.890304565429688</v>
+        <v>8.098221778869629</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7817,7 +7817,7 @@
         <v>20.70000076293945</v>
       </c>
       <c r="D444">
-        <v>18.53277015686035</v>
+        <v>16.85343170166016</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7831,7 +7831,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D445">
-        <v>6.22249174118042</v>
+        <v>7.099517822265625</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7845,7 +7845,7 @@
         <v>4</v>
       </c>
       <c r="D446">
-        <v>2.638017892837524</v>
+        <v>2.408129453659058</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7859,7 +7859,7 @@
         <v>34.79999923706055</v>
       </c>
       <c r="D447">
-        <v>17.25764274597168</v>
+        <v>14.89491367340088</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7873,7 +7873,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D448">
-        <v>2.032731533050537</v>
+        <v>2.383587837219238</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7887,7 +7887,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D449">
-        <v>6.6575026512146</v>
+        <v>5.281659126281738</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7901,7 +7901,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D450">
-        <v>2.247999668121338</v>
+        <v>2.405742645263672</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7915,7 +7915,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D451">
-        <v>14.97586727142334</v>
+        <v>13.40814876556396</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7929,7 +7929,7 @@
         <v>4</v>
       </c>
       <c r="D452">
-        <v>2.082766532897949</v>
+        <v>2.393656492233276</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7943,7 +7943,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D453">
-        <v>2.116740942001343</v>
+        <v>2.438479900360107</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7957,7 +7957,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D454">
-        <v>2.003118276596069</v>
+        <v>2.407222747802734</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7971,7 +7971,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D455">
-        <v>3.37283992767334</v>
+        <v>3.14513635635376</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7985,7 +7985,7 @@
         <v>33.5</v>
       </c>
       <c r="D456">
-        <v>22.85116195678711</v>
+        <v>20.81593322753906</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7999,7 +7999,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D457">
-        <v>2.278716087341309</v>
+        <v>2.376543045043945</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -8013,7 +8013,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D458">
-        <v>3.057414531707764</v>
+        <v>2.802646636962891</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -8027,7 +8027,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D459">
-        <v>2.736098289489746</v>
+        <v>2.840502738952637</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8041,7 +8041,7 @@
         <v>5</v>
       </c>
       <c r="D460">
-        <v>1.981786847114563</v>
+        <v>2.395962715148926</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8055,7 +8055,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D461">
-        <v>2.052802562713623</v>
+        <v>2.432248592376709</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8069,7 +8069,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D462">
-        <v>3.436698913574219</v>
+        <v>2.855668544769287</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8083,7 +8083,7 @@
         <v>2</v>
       </c>
       <c r="D463">
-        <v>3.60158109664917</v>
+        <v>2.399861335754395</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8097,7 +8097,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D464">
-        <v>1.959685206413269</v>
+        <v>2.383974075317383</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8111,7 +8111,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D465">
-        <v>9.257254600524902</v>
+        <v>10.61937046051025</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8125,7 +8125,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D466">
-        <v>2.091471672058105</v>
+        <v>2.414534091949463</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8139,7 +8139,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D467">
-        <v>2.135741233825684</v>
+        <v>2.393914937973022</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8153,7 +8153,7 @@
         <v>6.5</v>
       </c>
       <c r="D468">
-        <v>3.670524597167969</v>
+        <v>4.754795074462891</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8167,7 +8167,7 @@
         <v>14</v>
       </c>
       <c r="D469">
-        <v>3.702859878540039</v>
+        <v>3.239419460296631</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8181,7 +8181,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D470">
-        <v>3.139099597930908</v>
+        <v>2.84913444519043</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8195,7 +8195,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D471">
-        <v>2.082565307617188</v>
+        <v>2.382247924804688</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8209,7 +8209,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D472">
-        <v>5.037415981292725</v>
+        <v>3.263819217681885</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8223,7 +8223,7 @@
         <v>0.5</v>
       </c>
       <c r="D473">
-        <v>3.314009666442871</v>
+        <v>3.509352684020996</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8237,7 +8237,7 @@
         <v>5.5</v>
       </c>
       <c r="D474">
-        <v>6.389111995697021</v>
+        <v>5.718404769897461</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8251,7 +8251,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D475">
-        <v>13.87008571624756</v>
+        <v>11.39082431793213</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8265,7 +8265,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D476">
-        <v>5.183740615844727</v>
+        <v>6.293366432189941</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8279,7 +8279,7 @@
         <v>8.5</v>
       </c>
       <c r="D477">
-        <v>8.117534637451172</v>
+        <v>8.296896934509277</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8293,7 +8293,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D478">
-        <v>3.345087051391602</v>
+        <v>2.424674987792969</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8307,7 +8307,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D479">
-        <v>2.899996757507324</v>
+        <v>3.3032546043396</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8321,7 +8321,7 @@
         <v>5</v>
       </c>
       <c r="D480">
-        <v>2.079202175140381</v>
+        <v>2.411332368850708</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8335,7 +8335,7 @@
         <v>1.5</v>
       </c>
       <c r="D481">
-        <v>2.149930953979492</v>
+        <v>2.40434455871582</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8349,7 +8349,7 @@
         <v>6.5</v>
       </c>
       <c r="D482">
-        <v>6.439758777618408</v>
+        <v>3.695977687835693</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8363,7 +8363,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D483">
-        <v>2.066127300262451</v>
+        <v>2.429011344909668</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8377,7 +8377,7 @@
         <v>0.5</v>
       </c>
       <c r="D484">
-        <v>3.767405986785889</v>
+        <v>2.40531587600708</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8391,7 +8391,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D485">
-        <v>4.098322868347168</v>
+        <v>4.521037578582764</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8405,7 +8405,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D486">
-        <v>2.238558292388916</v>
+        <v>2.416447162628174</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8419,7 +8419,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D487">
-        <v>7.468501567840576</v>
+        <v>7.38005256652832</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8433,7 +8433,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D488">
-        <v>7.847755908966064</v>
+        <v>6.584419727325439</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8447,7 +8447,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>2.253865480422974</v>
+        <v>2.424532413482666</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8461,7 +8461,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D490">
-        <v>4.470356464385986</v>
+        <v>5.270566940307617</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8475,7 +8475,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D491">
-        <v>6.5942702293396</v>
+        <v>5.394091129302979</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8489,7 +8489,7 @@
         <v>5.5</v>
       </c>
       <c r="D492">
-        <v>2.315589904785156</v>
+        <v>2.408750534057617</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8503,7 +8503,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D493">
-        <v>1.95002806186676</v>
+        <v>2.407467365264893</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8517,7 +8517,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D494">
-        <v>2.134046792984009</v>
+        <v>2.49504280090332</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8531,7 +8531,7 @@
         <v>1</v>
       </c>
       <c r="D495">
-        <v>2.014540672302246</v>
+        <v>2.374663114547729</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8545,7 +8545,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D496">
-        <v>2.015204191207886</v>
+        <v>2.380961418151855</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8559,7 +8559,7 @@
         <v>14.30000019073486</v>
       </c>
       <c r="D497">
-        <v>10.00350570678711</v>
+        <v>8.374721527099609</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8573,7 +8573,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D498">
-        <v>4.687117099761963</v>
+        <v>3.601340293884277</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8587,7 +8587,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D499">
-        <v>2.196666240692139</v>
+        <v>2.873573780059814</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8601,7 +8601,7 @@
         <v>3.5</v>
       </c>
       <c r="D500">
-        <v>2.859408378601074</v>
+        <v>3.451569557189941</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8615,7 +8615,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D501">
-        <v>6.052812576293945</v>
+        <v>6.201460838317871</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8629,7 +8629,7 @@
         <v>10.5</v>
       </c>
       <c r="D502">
-        <v>6.506372928619385</v>
+        <v>5.34284496307373</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8643,7 +8643,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D503">
-        <v>5.621762275695801</v>
+        <v>4.5405592918396</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8657,7 +8657,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D504">
-        <v>2.036141157150269</v>
+        <v>2.377236604690552</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8671,7 +8671,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D505">
-        <v>5.308602809906006</v>
+        <v>4.982194900512695</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8685,7 +8685,7 @@
         <v>22</v>
       </c>
       <c r="D506">
-        <v>17.17829895019531</v>
+        <v>16.78575325012207</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8699,7 +8699,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D507">
-        <v>3.861680507659912</v>
+        <v>2.537303924560547</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8713,7 +8713,7 @@
         <v>4.5</v>
       </c>
       <c r="D508">
-        <v>3.229201316833496</v>
+        <v>2.457245826721191</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8727,7 +8727,7 @@
         <v>5.5</v>
       </c>
       <c r="D509">
-        <v>3.376336097717285</v>
+        <v>2.478763103485107</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8741,7 +8741,7 @@
         <v>6.5</v>
       </c>
       <c r="D510">
-        <v>10.27104377746582</v>
+        <v>11.43795108795166</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8755,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="D511">
-        <v>2.100822448730469</v>
+        <v>2.36506199836731</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8769,7 +8769,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D512">
-        <v>9.576374053955078</v>
+        <v>7.789725303649902</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8783,7 +8783,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D513">
-        <v>1.927491188049316</v>
+        <v>2.438656330108643</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8797,7 +8797,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D514">
-        <v>3.219867706298828</v>
+        <v>2.373347282409668</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8811,7 +8811,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D515">
-        <v>2.171250820159912</v>
+        <v>2.389623165130615</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8825,7 +8825,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D516">
-        <v>2.840853214263916</v>
+        <v>2.371619701385498</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8839,7 +8839,7 @@
         <v>25.60000038146973</v>
       </c>
       <c r="D517">
-        <v>9.623575210571289</v>
+        <v>10.65698909759521</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8853,7 +8853,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D518">
-        <v>6.535043239593506</v>
+        <v>6.676867485046387</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8867,7 +8867,7 @@
         <v>3.5</v>
       </c>
       <c r="D519">
-        <v>2.096195220947266</v>
+        <v>2.369458198547363</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8881,7 +8881,7 @@
         <v>4.5</v>
       </c>
       <c r="D520">
-        <v>7.655119895935059</v>
+        <v>8.763742446899414</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8895,7 +8895,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D521">
-        <v>3.353107452392578</v>
+        <v>7.308845043182373</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8909,7 +8909,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D522">
-        <v>2.549663066864014</v>
+        <v>2.525011539459229</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8923,7 +8923,7 @@
         <v>13.39999961853027</v>
       </c>
       <c r="D523">
-        <v>6.948810577392578</v>
+        <v>6.576362609863281</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8937,7 +8937,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="D524">
-        <v>11.37114143371582</v>
+        <v>11.20814609527588</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8951,7 +8951,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D525">
-        <v>5.736591815948486</v>
+        <v>9.915414810180664</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8965,7 +8965,7 @@
         <v>16.79999923706055</v>
       </c>
       <c r="D526">
-        <v>14.42175006866455</v>
+        <v>13.69698524475098</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8979,7 +8979,7 @@
         <v>4</v>
       </c>
       <c r="D527">
-        <v>2.026256084442139</v>
+        <v>2.387594223022461</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8993,7 +8993,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D528">
-        <v>3.746382236480713</v>
+        <v>3.265324115753174</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9007,7 +9007,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D529">
-        <v>2.160025119781494</v>
+        <v>2.418179988861084</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -9021,7 +9021,7 @@
         <v>33.29999923706055</v>
       </c>
       <c r="D530">
-        <v>20.69519805908203</v>
+        <v>18.63388252258301</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9035,7 +9035,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D531">
-        <v>2.18212628364563</v>
+        <v>5.887182235717773</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9049,7 +9049,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D532">
-        <v>4.644302845001221</v>
+        <v>4.453325748443604</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9063,7 +9063,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D533">
-        <v>10.83727550506592</v>
+        <v>10.97849369049072</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9077,7 +9077,7 @@
         <v>23.10000038146973</v>
       </c>
       <c r="D534">
-        <v>16.90783309936523</v>
+        <v>17.76194190979004</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9091,7 +9091,7 @@
         <v>13.89999961853027</v>
       </c>
       <c r="D535">
-        <v>5.738921642303467</v>
+        <v>2.697726726531982</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9105,7 +9105,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D536">
-        <v>2.081710338592529</v>
+        <v>2.396028518676758</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9119,7 +9119,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D537">
-        <v>5.603857517242432</v>
+        <v>5.794960021972656</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9133,7 +9133,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D538">
-        <v>2.073703289031982</v>
+        <v>2.427117347717285</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9147,7 +9147,7 @@
         <v>11.5</v>
       </c>
       <c r="D539">
-        <v>6.276949405670166</v>
+        <v>4.082983493804932</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9161,7 +9161,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D540">
-        <v>1.974918365478516</v>
+        <v>6.421811103820801</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9175,7 +9175,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D541">
-        <v>1.932186245918274</v>
+        <v>2.400682926177979</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9189,7 +9189,7 @@
         <v>55.20000076293945</v>
       </c>
       <c r="D542">
-        <v>40.59329986572266</v>
+        <v>35.84726715087891</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9203,7 +9203,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D543">
-        <v>9.727775573730469</v>
+        <v>7.816198348999023</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9217,7 +9217,7 @@
         <v>8</v>
       </c>
       <c r="D544">
-        <v>3.136335611343384</v>
+        <v>2.411131858825684</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9231,7 +9231,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D545">
-        <v>7.725306034088135</v>
+        <v>6.659245491027832</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9245,7 +9245,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D546">
-        <v>2.523324012756348</v>
+        <v>2.378429412841797</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9259,7 +9259,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D547">
-        <v>3.313938140869141</v>
+        <v>4.751477718353271</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9273,7 +9273,7 @@
         <v>16.39999961853027</v>
       </c>
       <c r="D548">
-        <v>6.59273624420166</v>
+        <v>6.211960315704346</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9287,7 +9287,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D549">
-        <v>4.013140201568604</v>
+        <v>2.4315185546875</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9301,7 +9301,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D550">
-        <v>5.473430156707764</v>
+        <v>5.56362771987915</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9315,7 +9315,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D551">
-        <v>1.974161267280579</v>
+        <v>2.422411918640137</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9329,7 +9329,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>6.377501487731934</v>
+        <v>3.839915752410889</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9343,7 +9343,7 @@
         <v>1</v>
       </c>
       <c r="D553">
-        <v>2.638479232788086</v>
+        <v>2.405487537384033</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9357,7 +9357,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D554">
-        <v>4.859150409698486</v>
+        <v>2.796022415161133</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9371,7 +9371,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D555">
-        <v>3.156466007232666</v>
+        <v>3.003676414489746</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9385,7 +9385,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D556">
-        <v>3.292975902557373</v>
+        <v>2.527689933776855</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9399,7 +9399,7 @@
         <v>5.5</v>
       </c>
       <c r="D557">
-        <v>2.733399868011475</v>
+        <v>2.418282985687256</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9413,7 +9413,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D558">
-        <v>4.167605400085449</v>
+        <v>3.231035709381104</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9427,7 +9427,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D559">
-        <v>2.098674058914185</v>
+        <v>2.363012313842773</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9441,7 +9441,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D560">
-        <v>2.8747239112854</v>
+        <v>2.545234203338623</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9455,7 +9455,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D561">
-        <v>2.067275762557983</v>
+        <v>2.39189624786377</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9469,7 +9469,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D562">
-        <v>1.94895076751709</v>
+        <v>2.39828085899353</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9483,7 +9483,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D563">
-        <v>3.065294504165649</v>
+        <v>3.302961826324463</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9497,7 +9497,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D564">
-        <v>6.126325130462646</v>
+        <v>5.332873821258545</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9511,7 +9511,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D565">
-        <v>8.385408401489258</v>
+        <v>5.386007308959961</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9525,7 +9525,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D566">
-        <v>3.836203098297119</v>
+        <v>2.459722995758057</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9539,7 +9539,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D567">
-        <v>10.88217735290527</v>
+        <v>10.210524559021</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9553,7 +9553,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D568">
-        <v>1.891590356826782</v>
+        <v>2.392260313034058</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9567,7 +9567,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D569">
-        <v>2.070262432098389</v>
+        <v>2.402198791503906</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9581,7 +9581,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D570">
-        <v>11.72863578796387</v>
+        <v>11.5273380279541</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9595,7 +9595,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D571">
-        <v>4.026183128356934</v>
+        <v>2.45393180847168</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9609,7 +9609,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D572">
-        <v>2.233845472335815</v>
+        <v>2.441520214080811</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9623,7 +9623,7 @@
         <v>1</v>
       </c>
       <c r="D573">
-        <v>2.006804943084717</v>
+        <v>2.377590656280518</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9637,7 +9637,7 @@
         <v>1.5</v>
       </c>
       <c r="D574">
-        <v>2.06099796295166</v>
+        <v>2.368670463562012</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9651,7 +9651,7 @@
         <v>3.5</v>
       </c>
       <c r="D575">
-        <v>2.345712184906006</v>
+        <v>2.44269323348999</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9665,7 +9665,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D576">
-        <v>2.014242172241211</v>
+        <v>2.412160873413086</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9679,7 +9679,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D577">
-        <v>8.074950218200684</v>
+        <v>7.745245456695557</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9693,7 +9693,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D578">
-        <v>9.170989036560059</v>
+        <v>7.702432632446289</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9707,7 +9707,7 @@
         <v>23.39999961853027</v>
       </c>
       <c r="D579">
-        <v>15.11244106292725</v>
+        <v>17.45384979248047</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9721,7 +9721,7 @@
         <v>10</v>
       </c>
       <c r="D580">
-        <v>4.412847518920898</v>
+        <v>8.295170783996582</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9735,7 +9735,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D581">
-        <v>2.886317253112793</v>
+        <v>2.430051803588867</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9749,7 +9749,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D582">
-        <v>2.045334577560425</v>
+        <v>2.403725624084473</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9763,7 +9763,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D583">
-        <v>15.77039909362793</v>
+        <v>17.0462589263916</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9777,7 +9777,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D584">
-        <v>3.547469139099121</v>
+        <v>2.553561925888062</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9791,7 +9791,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D585">
-        <v>7.078522205352783</v>
+        <v>7.255460262298584</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9805,7 +9805,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D586">
-        <v>12.37136650085449</v>
+        <v>10.44287586212158</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9819,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="D587">
-        <v>2.062641620635986</v>
+        <v>2.414682388305664</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9833,7 +9833,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D588">
-        <v>2.444069385528564</v>
+        <v>2.384790897369385</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9847,7 +9847,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D589">
-        <v>6.728482246398926</v>
+        <v>6.597079277038574</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9861,7 +9861,7 @@
         <v>1</v>
       </c>
       <c r="D590">
-        <v>1.929738521575928</v>
+        <v>2.39670467376709</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9875,7 +9875,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D591">
-        <v>4.760132312774658</v>
+        <v>2.862500667572021</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9889,7 +9889,7 @@
         <v>21.10000038146973</v>
       </c>
       <c r="D592">
-        <v>26.74067115783691</v>
+        <v>23.32024574279785</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9903,7 +9903,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D593">
-        <v>2.031407594680786</v>
+        <v>2.401132822036743</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9917,7 +9917,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D594">
-        <v>3.855330944061279</v>
+        <v>2.380595445632935</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9931,7 +9931,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D595">
-        <v>1.968197703361511</v>
+        <v>2.469917297363281</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9945,7 +9945,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D596">
-        <v>2.081881046295166</v>
+        <v>2.3789381980896</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9959,7 +9959,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D597">
-        <v>9.460494995117188</v>
+        <v>11.54016971588135</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9973,7 +9973,7 @@
         <v>2</v>
       </c>
       <c r="D598">
-        <v>2.597765445709229</v>
+        <v>2.405848503112793</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9987,7 +9987,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D599">
-        <v>2.056702852249146</v>
+        <v>2.399085998535156</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -10001,7 +10001,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D600">
-        <v>3.56449031829834</v>
+        <v>6.013639450073242</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -10015,7 +10015,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D601">
-        <v>2.022730827331543</v>
+        <v>2.346102714538574</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -10029,7 +10029,7 @@
         <v>18.39999961853027</v>
       </c>
       <c r="D602">
-        <v>12.80303955078125</v>
+        <v>13.07068920135498</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10043,7 +10043,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D603">
-        <v>4.08103084564209</v>
+        <v>4.772425651550293</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10057,7 +10057,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D604">
-        <v>2.874733924865723</v>
+        <v>2.416311740875244</v>
       </c>
     </row>
   </sheetData>
